--- a/编程/数据集/整合版数据.xlsx
+++ b/编程/数据集/整合版数据.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\数模校赛\Mm\编程\数据集\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B44D5E3-3670-4935-A5FF-7956FDD5665F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADC4CCE0-DF3E-4FD5-B15D-4DD539B1C0AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -72,15 +72,15 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>义务教育招生数/万人</t>
+    <t>义务教育学校数</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>高中教育招生数/万人</t>
+    <t>高中教育学校数</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>高等教育招生数/万人</t>
+    <t>高等教育学校数</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -91,7 +91,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -135,6 +135,13 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -159,7 +166,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
@@ -169,6 +176,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -466,6 +479,9 @@
     <col min="10" max="10" width="28.44140625" customWidth="1"/>
     <col min="11" max="11" width="21.33203125" customWidth="1"/>
     <col min="12" max="12" width="20.21875" customWidth="1"/>
+    <col min="13" max="13" width="17" customWidth="1"/>
+    <col min="14" max="14" width="18.109375" customWidth="1"/>
+    <col min="15" max="15" width="17.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -487,13 +503,13 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="6" t="s">
         <v>11</v>
       </c>
       <c r="J1" s="3" t="s">
@@ -525,14 +541,14 @@
       <c r="F2" s="1">
         <v>55.74</v>
       </c>
-      <c r="G2" s="2">
-        <v>68.783199999999994</v>
-      </c>
-      <c r="H2" s="2">
-        <v>21.218599999999999</v>
-      </c>
-      <c r="I2" s="2">
-        <v>18.893000000000001</v>
+      <c r="G2">
+        <v>10158</v>
+      </c>
+      <c r="H2">
+        <v>545</v>
+      </c>
+      <c r="I2">
+        <v>58</v>
       </c>
       <c r="J2" s="2">
         <v>200.68610000000001</v>
@@ -563,14 +579,14 @@
       <c r="F3">
         <v>56.81</v>
       </c>
-      <c r="G3" s="2">
-        <v>64.525400000000005</v>
-      </c>
-      <c r="H3" s="2">
-        <v>17.584599999999998</v>
-      </c>
-      <c r="I3" s="2">
-        <v>19.424600000000002</v>
+      <c r="G3">
+        <v>10087</v>
+      </c>
+      <c r="H3">
+        <v>539</v>
+      </c>
+      <c r="I3">
+        <v>58</v>
       </c>
       <c r="J3" s="2">
         <v>189.1687</v>
@@ -601,14 +617,14 @@
       <c r="F4">
         <v>57.64</v>
       </c>
-      <c r="G4" s="2">
-        <v>62.288499999999999</v>
-      </c>
-      <c r="H4" s="2">
-        <v>18.065999999999999</v>
-      </c>
-      <c r="I4" s="2">
-        <v>19.456600000000002</v>
+      <c r="G4">
+        <v>9895</v>
+      </c>
+      <c r="H4">
+        <v>528</v>
+      </c>
+      <c r="I4">
+        <v>58</v>
       </c>
       <c r="J4" s="2">
         <v>187.5284</v>
@@ -639,14 +655,14 @@
       <c r="F5">
         <v>58.75</v>
       </c>
-      <c r="G5" s="2">
-        <v>64.9255</v>
-      </c>
-      <c r="H5" s="2">
-        <v>18.6492</v>
-      </c>
-      <c r="I5" s="2">
-        <v>19.898199999999999</v>
+      <c r="G5">
+        <v>9635</v>
+      </c>
+      <c r="H5">
+        <v>518</v>
+      </c>
+      <c r="I5">
+        <v>60</v>
       </c>
       <c r="J5" s="2">
         <v>186.84880000000001</v>
@@ -677,14 +693,14 @@
       <c r="F6">
         <v>59.71</v>
       </c>
-      <c r="G6" s="2">
-        <v>63.026600000000002</v>
-      </c>
-      <c r="H6" s="2">
-        <v>18.627099999999999</v>
-      </c>
-      <c r="I6" s="2">
-        <v>20.1783</v>
+      <c r="G6">
+        <v>9428</v>
+      </c>
+      <c r="H6">
+        <v>518</v>
+      </c>
+      <c r="I6">
+        <v>62</v>
       </c>
       <c r="J6" s="2">
         <v>184.6909</v>
@@ -715,14 +731,14 @@
       <c r="F7">
         <v>60.85</v>
       </c>
-      <c r="G7" s="2">
-        <v>61.405200000000001</v>
-      </c>
-      <c r="H7" s="2">
-        <v>16.419599999999999</v>
-      </c>
-      <c r="I7" s="2">
-        <v>21.167100000000001</v>
+      <c r="G7">
+        <v>8713</v>
+      </c>
+      <c r="H7">
+        <v>508</v>
+      </c>
+      <c r="I7">
+        <v>62</v>
       </c>
       <c r="J7" s="2">
         <v>186.25069999999999</v>
@@ -753,14 +769,14 @@
       <c r="F8">
         <v>61.63</v>
       </c>
-      <c r="G8" s="2">
-        <v>56.404000000000003</v>
-      </c>
-      <c r="H8" s="2">
-        <v>19.3277</v>
-      </c>
-      <c r="I8" s="2">
-        <v>24.510400000000001</v>
+      <c r="G8">
+        <v>8571</v>
+      </c>
+      <c r="H8">
+        <v>506</v>
+      </c>
+      <c r="I8">
+        <v>62</v>
       </c>
       <c r="J8" s="2">
         <v>184.02189999999999</v>
@@ -791,14 +807,14 @@
       <c r="F9">
         <v>62.64</v>
       </c>
-      <c r="G9" s="2">
-        <v>51.433300000000003</v>
-      </c>
-      <c r="H9" s="2">
-        <v>19.633099999999999</v>
-      </c>
-      <c r="I9" s="2">
-        <v>23.8127</v>
+      <c r="G9">
+        <v>8550</v>
+      </c>
+      <c r="H9">
+        <v>501</v>
+      </c>
+      <c r="I9">
+        <v>64</v>
       </c>
       <c r="J9" s="2">
         <v>180.99590000000001</v>
@@ -829,14 +845,14 @@
       <c r="F10">
         <v>63.36</v>
       </c>
-      <c r="G10" s="2">
-        <v>49.490900000000003</v>
-      </c>
-      <c r="H10" s="2">
-        <v>19.9696</v>
-      </c>
-      <c r="I10" s="2">
-        <v>24.933700000000002</v>
+      <c r="G10">
+        <v>8421</v>
+      </c>
+      <c r="H10">
+        <v>504</v>
+      </c>
+      <c r="I10">
+        <v>66</v>
       </c>
       <c r="J10" s="2">
         <v>175.2226</v>
@@ -867,14 +883,14 @@
       <c r="F11">
         <v>63.73</v>
       </c>
-      <c r="G11" s="2">
-        <v>47.351599999999998</v>
-      </c>
-      <c r="H11" s="2">
-        <v>19.3917</v>
-      </c>
-      <c r="I11" s="2">
-        <v>28.739000000000001</v>
+      <c r="G11">
+        <v>7606</v>
+      </c>
+      <c r="H11">
+        <v>503</v>
+      </c>
+      <c r="I11">
+        <v>66</v>
       </c>
       <c r="J11" s="2">
         <v>170.38640000000001</v>
@@ -905,14 +921,14 @@
       <c r="F12">
         <v>64.72</v>
       </c>
-      <c r="G12" s="2">
-        <v>44.872900000000001</v>
-      </c>
-      <c r="H12" s="2">
-        <v>17.4209</v>
-      </c>
-      <c r="I12" s="2">
-        <v>27.484100000000002</v>
+      <c r="G12">
+        <v>6322</v>
+      </c>
+      <c r="H12">
+        <v>478</v>
+      </c>
+      <c r="I12">
+        <v>66</v>
       </c>
       <c r="J12" s="2">
         <v>168.6234</v>
